--- a/artfynd/A 26956-2023 artfynd.xlsx
+++ b/artfynd/A 26956-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 26956-2023 artfynd.xlsx
+++ b/artfynd/A 26956-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110601410</v>
+        <v>118726563</v>
       </c>
       <c r="B2" t="n">
-        <v>98535</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>100070</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flakaryd, Bl</t>
+          <t>Svalemåla, Bl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505243.0858920306</v>
+        <v>505462</v>
       </c>
       <c r="R2" t="n">
-        <v>6225468.06170741</v>
+        <v>6225445</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,27 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-07-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-07-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Blad av blåsippor</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,27 +766,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johannes Holswilder</t>
+          <t>Lutz Eckstein</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johannes Holswilder</t>
+          <t>Lutz Eckstein</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110600989</v>
+        <v>98336540</v>
       </c>
       <c r="B3" t="n">
-        <v>98535</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,41 +789,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>101246</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flakaryd, Bl</t>
+          <t>Kullerydsvägen, Bl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505108.221074445</v>
+        <v>505451</v>
       </c>
       <c r="R3" t="n">
-        <v>6225377.732524289</v>
+        <v>6225439</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,27 +857,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-07-04</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-07-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Blad av blåsippor intill mossklädd låga</t>
+          <t>Ekoxeuppropet 2020. gående</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,66 +876,65 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johannes Holswilder</t>
+          <t>Monika Sunhede</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johannes Holswilder</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Via Monika Sunhede</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Ekoxeuppropet 2020</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110647334</v>
+        <v>110650626</v>
       </c>
       <c r="B4" t="n">
-        <v>98535</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>101312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Molnfläcksbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Mesosa nebulosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fabricius, 1781)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -971,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505307.8627298978</v>
+        <v>505079</v>
       </c>
       <c r="R4" t="n">
-        <v>6225404.134845529</v>
+        <v>6225329</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,27 +972,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-04</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Fem blåsippeblad i bokskog</t>
+          <t>Karaktäristiskt cirkelrunt kläckhål med diameter av 6 mm på den grövsta stammen i hasselbusken.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,15 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110650626</v>
+        <v>110647489</v>
       </c>
       <c r="B5" t="n">
-        <v>5248</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5178</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1065,21 +1021,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101312</v>
+        <v>102204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Molnfläcksbock</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Mesosa nebulosa</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fabricius, 1781)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1098,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505078.7178145887</v>
+        <v>505356</v>
       </c>
       <c r="R5" t="n">
-        <v>6225329.274075666</v>
+        <v>6225564</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,27 +1084,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-07-04</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-07-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Karaktäristiskt cirkelrunt kläckhål med diameter av 6 mm på den grövsta stammen i hasselbusken.</t>
+          <t>Äldre gnagspår och kläckhål av grönhjon på flera grenar av vindfälle gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1173,6 +1119,335 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>110600989</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Flakaryd, Bl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>505109</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6225377</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-07-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-07-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Blad av blåsippor intill mossklädd låga</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Johannes Holswilder</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Johannes Holswilder</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>110601410</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Flakaryd, Bl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>505243</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6225468</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-07-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-07-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Blad av blåsippor</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Johannes Holswilder</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Johannes Holswilder</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>110647334</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Flakaryd, Bl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>505308</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6225404</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Fem blåsippeblad i bokskog</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Johannes Holswilder</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Johannes Holswilder</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26956-2023 artfynd.xlsx
+++ b/artfynd/A 26956-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1258,57 +1258,52 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110647489</v>
+        <v>136133380</v>
       </c>
       <c r="B7" t="n">
-        <v>5178</v>
+        <v>9417</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102204</v>
+        <v>101246</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Flakaryd, Bl</t>
+          <t>Kullerydsvägen 14, Bl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505356</v>
+        <v>505487</v>
       </c>
       <c r="R7" t="n">
-        <v>6225564</v>
+        <v>6225466</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1332,17 +1327,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>20:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>20:31</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Äldre gnagspår och kläckhål av grönhjon på flera grenar av vindfälle gran.</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,66 +1356,66 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johannes Holswilder</t>
+          <t>Monika Sunhede</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johannes Holswilder</t>
+          <t>Via Monika Sunhede</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110647489</t>
+          <t>https://artportalen.se/Sighting/136133380</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110601410</v>
+        <v>110647489</v>
       </c>
       <c r="B8" t="n">
-        <v>101326</v>
+        <v>5178</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>102204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1418,10 +1423,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505243</v>
+        <v>505356</v>
       </c>
       <c r="R8" t="n">
-        <v>6225468</v>
+        <v>6225564</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,17 +1453,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-07-04</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-07-04</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Blad av blåsippor</t>
+          <t>Äldre gnagspår och kläckhål av grönhjon på flera grenar av vindfälle gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,6 +1489,122 @@
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110647489</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>110601410</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Flakaryd, Bl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>505243</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6225468</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-07-04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-07-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Blad av blåsippor</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Johannes Holswilder</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Johannes Holswilder</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/110601410</t>
         </is>
@@ -1498,6 +1619,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26956-2023 artfynd.xlsx
+++ b/artfynd/A 26956-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1379,57 +1379,52 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110647489</v>
+        <v>136335374</v>
       </c>
       <c r="B8" t="n">
-        <v>5178</v>
+        <v>9417</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102204</v>
+        <v>101246</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Flakaryd, Bl</t>
+          <t>Båknaberget, Bl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505356</v>
+        <v>505163</v>
       </c>
       <c r="R8" t="n">
-        <v>6225564</v>
+        <v>6225461</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1453,17 +1448,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Äldre gnagspår och kläckhål av grönhjon på flera grenar av vindfälle gran.</t>
+          <t>levande hane</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,66 +1477,66 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johannes Holswilder</t>
+          <t>Monika Sunhede</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johannes Holswilder</t>
+          <t>Via Monika Sunhede</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110647489</t>
+          <t>https://artportalen.se/Sighting/136335374</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110601410</v>
+        <v>110647489</v>
       </c>
       <c r="B9" t="n">
-        <v>101326</v>
+        <v>5178</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>102204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1539,10 +1544,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505243</v>
+        <v>505356</v>
       </c>
       <c r="R9" t="n">
-        <v>6225468</v>
+        <v>6225564</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,17 +1574,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-07-04</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-07-04</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Blad av blåsippor</t>
+          <t>Äldre gnagspår och kläckhål av grönhjon på flera grenar av vindfälle gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1605,6 +1610,122 @@
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110647489</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>110601410</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Flakaryd, Bl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>505243</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6225468</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-07-04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-07-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Blad av blåsippor</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Johannes Holswilder</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Johannes Holswilder</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/110601410</t>
         </is>
@@ -1620,6 +1741,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
